--- a/engine/publish_queue/PHAR/EIPICO_Valuation_Model_09082026.xlsx
+++ b/engine/publish_queue/PHAR/EIPICO_Valuation_Model_09082026.xlsx
@@ -2780,19 +2780,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>48.10850731158106</v>
+        <v>45.68528385393408</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>39.77511325126461</v>
+        <v>37.81150099018128</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>27.37925743745052</v>
+        <v>26.01416352323024</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>22.64818890004397</v>
+        <v>21.4844134990437</v>
       </c>
     </row>
     <row r="7">
@@ -2824,19 +2824,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>23.88951618644536</v>
+        <v>22.8494533223467</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>25.60843732759319</v>
+        <v>24.47046167069734</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>27.62520707737693</v>
+        <v>26.3649795393194</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>30.03879318326904</v>
+        <v>28.621995629933</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
     </row>
     <row r="10">
@@ -2852,7 +2852,7 @@
         <v>0.55</v>
       </c>
       <c r="D10" s="51" t="n">
-        <v>0.629</v>
+        <v>0.6658188407423365</v>
       </c>
       <c r="E10" s="51" t="n">
         <v>0.75</v>
@@ -2874,7 +2874,7 @@
         <v>36.76279124931227</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>27.93707835693304</v>
@@ -2912,19 +2912,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>51.3465182256518</v>
+        <v>49.26491319840814</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>44.67413728650396</v>
+        <v>42.7590534998364</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>24.65699446906032</v>
+        <v>23.24147440412117</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>14.64842306033853</v>
+        <v>13.4826848562636</v>
       </c>
     </row>
     <row r="16">
@@ -2956,19 +2956,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>46.55399859968628</v>
+        <v>44.63956596764732</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>39.77573462134068</v>
+        <v>38.00668249749155</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>26.21920666464951</v>
+        <v>24.74091555718003</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>19.440942686304</v>
+        <v>18.10803208702435</v>
       </c>
     </row>
     <row r="19">
@@ -3000,19 +3000,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>39.06699370892114</v>
+        <v>37.36532565503385</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>36.13260099179308</v>
+        <v>34.4684633681824</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>29.65057380959478</v>
+        <v>28.0704744073638</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>26.08047464187032</v>
+        <v>24.54723077671931</v>
       </c>
     </row>
     <row r="22">
@@ -3044,19 +3044,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>38.5893686066067</v>
+        <v>36.77869012904124</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>35.22839062070677</v>
+        <v>33.53006026952217</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>30.56624626531026</v>
+        <v>29.02402305899556</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>27.69837601691766</v>
+        <v>26.252358655231</v>
       </c>
     </row>
     <row r="25">
@@ -3088,19 +3088,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>32.70054369639525</v>
+        <v>31.34494284548571</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>35.41663310005087</v>
+        <v>33.89811072289919</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>38.71262822213044</v>
+        <v>36.98163985573206</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>42.81928419703347</v>
+        <v>40.80133138880694</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>48.10850731158106</v>
+        <v>45.68528385393408</v>
       </c>
     </row>
     <row r="27">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>27.99471779162108</v>
+        <v>26.81224996276908</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>30.14854174524684</v>
+        <v>28.8405802906386</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>32.71624170205939</v>
+        <v>31.24838047980015</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>35.84770130865045</v>
+        <v>34.1699621733944</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>39.77511325126461</v>
+        <v>37.81150099018128</v>
       </c>
     </row>
     <row r="28">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>23.88951618644536</v>
+        <v>22.8494533223467</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>25.60843732759319</v>
+        <v>24.47046167069734</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>27.62520707737693</v>
+        <v>26.3649795393194</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>30.03879318326904</v>
+        <v>28.621995629933</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>32.99747064299516</v>
+        <v>31.37379902733586</v>
       </c>
     </row>
     <row r="29">
@@ -3154,19 +3154,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>20.27933441741304</v>
+        <v>19.35781412337375</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>21.65769560796352</v>
+        <v>20.65893665542676</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>23.25138341859161</v>
+        <v>22.15790078568526</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>25.12649378224442</v>
+        <v>23.9142656428088</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>27.37925743745052</v>
+        <v>26.01416352323024</v>
       </c>
     </row>
     <row r="30">
@@ -3176,19 +3176,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>17.08186047120632</v>
+        <v>16.26006785654848</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>18.19069765675845</v>
+        <v>17.3073954172165</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>19.45530089136148</v>
+        <v>18.49776590833174</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>20.9200982649097</v>
+        <v>19.87124732344099</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>22.64818890004397</v>
+        <v>21.4844134990437</v>
       </c>
     </row>
     <row r="32">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B33" s="19" t="n">
-        <v>8870.715521684808</v>
+        <v>9321.885127781243</v>
       </c>
     </row>
     <row r="34">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.3228209742828306</v>
+        <v>0.3337598757730512</v>
       </c>
     </row>
     <row r="35">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>126.5186435454996</v>
+        <v>132.9534532778984</v>
       </c>
     </row>
     <row r="36">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B36" s="24" t="n">
-        <v>1.265186435454996</v>
+        <v>1.329534532778984</v>
       </c>
     </row>
   </sheetData>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 80% of core enterprise value, 61% of total</t>
+          <t>Terminal value 79% of core enterprise value, 61% of total</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 80% of core enterprise value, 65% of total</t>
+          <t>Terminal value 79% of core enterprise value, 64% of total</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Justified 1.19 times book</t>
+          <t>Justified 1.16 times book</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="C49" s="22" t="n">
-        <v>0.629</v>
+        <v>0.6658188407423365</v>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
